--- a/data/rubble-transfer/plan.xlsx
+++ b/data/rubble-transfer/plan.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="223" documentId="11_A6BF2E2CF2CA68D323205908F6291AA03A305B13" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34770786-0C71-4BFE-AB74-D7180BF44DC6}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beyazsapkalilar-my.sharepoint.com/personal/modar_g_med_gov_sy/Documents/إدارة تقييم الأضرار والتعافي/ملفات تتبع مشاريع الأنقاض/تقرير سير العمل للمراحل الثلاث/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BA1FDA8-6B1E-4EC8-A18A-8D9A5BC11651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
@@ -84,16 +89,16 @@
     <t>تم استخدام الكميات المتبقية من ساعات عمل الاليات ومعادلتها بسعر ترحيل الأنقاض</t>
   </si>
   <si>
-    <t>دير الزور</t>
-  </si>
-  <si>
-    <t>ارسلت الشركة السورية للتشييد والبناء(المقاول)كتابا بالسعر الجديد بزيادة 50% عن السعر القديم وتم ارسال العرض الجديد من الدعم التنفيذي الى القسم المالي لدراسته كما تم ارسال نسخة من العرض الى السيد معاون الوزير وبانتظار الموافقات على الاسعار الجديدة للبدء بالمشروع</t>
+    <t>ريف دير الزور</t>
+  </si>
+  <si>
+    <t>سيتم الاجتماع اليوم 25/10/2026 مع الشركة المنفذة لتحديد الية العمل-تم الرد من قبل الشركة المنفذة حيث تم اسناد الامر لوزارة الاشغال العامة والاسكان لتتواصل مع وزارة الطوارئ وادارة الكوارث</t>
   </si>
   <si>
     <t>تم الانتهاء من العمل في مناطق معرة النعمان ومركز ادلب وخان شيخون وجسر الشغور ولا زال العمل جاري في اريحا</t>
   </si>
   <si>
-    <t>العمل متوقف اليوم في كل المواقع بسبب سوء الاحوال الجوية وخطورة الطرق</t>
+    <t>تم التوقف بتاريخ 6/10/2026 الساعة 11:00 صباحا نظرا لسوء الاحوال الجوية وتم استئناف العمل , توقف العمل بتاريخ 12/10/2026 بستة مواقع من اصل تسعة مواقع بسبب عدم توفر الاليات ومازوت للاليات وبتاريخ 13-14/ 10 /2026 يوجد توقف في 7 مناطق بسبب عدم توفر المازوت وتم ارسال كتاب تبرير من المقاول بتاريخ 14/10/2026 الى مديرية اللاذقية للنظر بالاسباب واحتسابها كمدة مبررة. انخفاض الانتاجية وتوقف العمل ببعض المناطق بتاريخ 21-22/10/2026 بسبب انقطاع مادة المازوت-انتهاء مدة العقد بتاريخ 25/10/2026 وتم رفع كتاب تبرير من قبل المقاول لتبرير الايام التي تم التوقف فيها عن العمل</t>
   </si>
   <si>
     <t xml:space="preserve">اجمالي المرحلة الثانية </t>
@@ -105,36 +110,40 @@
     <t>درعا</t>
   </si>
   <si>
-    <t xml:space="preserve">بعد الانتهاء من اعلان المناقصة تم تقديم عرض واحد فقط لمقاول واحد فقط في منطقة درعا </t>
+    <t>تم فض عروض لمنطقتين لكن السعر غير مناسب وتم ارسال العروض الى الدعم التنفيذي للتفاوض مع المقاولين</t>
   </si>
   <si>
     <t>ريف دمشق</t>
   </si>
   <si>
-    <t>في مرحلة فض العروض وبانتظار موافقة الوزير على طلب كتاب العقد بالتراضي علما انه قد تم رفع الطلب منذ الاربعاء الماضي بتاريخ 30/9/2026
-سيتم اجراء مقابلات لاستقطاب الكادر الهندسي وستبدا المقابلات اعتبارا من الغد بتاريخ 5/10/2026</t>
-  </si>
-  <si>
-    <t>تم الانتهاء من تقديم العروض من قبل المقاولين بعد الانتهاء من اعلان المناقصة وتم ترشيح 
-اسماء كادر هندسي ليتم اجراء مقابلات معهم وانطلاق المشروع حيث من المتوقع انطلاق المشروع بداية 
-1/11/2026</t>
+    <t>سيتم غدا الاربعاء 28/10/2026 افتتاح المشروع في منطقة حرستا حي العجمي</t>
+  </si>
+  <si>
+    <t>من المتوقع البدء بالمشروع بداية الاسبوع القادم</t>
   </si>
   <si>
     <t>حمص</t>
   </si>
   <si>
-    <t xml:space="preserve">تم الانتهاء من المعاينة البصرية  لمسح المخلفات الحربية ولكن سيبقى فريق  من ال UXOموجود اثناء العمل مع الفريق الميداني  لضمان الامن وسلامة العمال 
-جاري العمل على اجراء المقابلات واستقطاب الكادر الهندسي بالتنسيق مع التنمية 
-اليوم هو اخر موعد لاعلان المناقصة وانتهاء التقديم </t>
-  </si>
-  <si>
-    <t xml:space="preserve">تم توقف الاعمال في جبل سمعان بتاريخ 3/10 بسبب الامطار وسوء احوال الطقس وكان العمل مستمر في منطقة اعزاز
+    <t>يتم التفاوض مع المقاولين لتقدير كمية الوقود اللازمة للمشروع</t>
+  </si>
+  <si>
+    <t>تم توقف الاعمال في جبل سمعان بتاريخ 3/10 بسبب الامطار وسوء احوال الطقس وكان العمل مستمر في منطقة اعزاز
 تم استئناف العمل في جبل سمعان بتاريخ 4/10 بعد توقف الامطار 
- العمل جاري في اعزاز ومنطقة جبل سمعان </t>
-  </si>
-  <si>
-    <t xml:space="preserve">تم الانتهاء من تقديم عروض المقاولين لمنطقة معرة النعمان وخان شيخون وهم في مرحلة فض العروض 
-اما بالنسبة لجسر الشغور وادلب فالعقود بمجلس تدقيق الدولة </t>
+تم توقف الاعمال بشكل نهائي من قبل مقاولين اعزاز وجبل سمعان منذ تاريخ 7/10/2026 ولغاية تاريخ اليوم 15/10/2026 مازال العمل 
+متوقفا وذلك للاسباب التاليه:
+1.التأخير بتصديق العقد حتى هذا التاريخ حيث بدأت الأعمال في اعزاز  بتاريخ 1/9/2026   وبلغت نسبة الإنجاز للمشروع أكثر من 33% وبحاجة إلى صرف المستحقات المالية لقاء هذه الأعمال 
+2- ارتفاع أسعار المحروقات بنسبة 40%
+1- التأخير بتصديق العقد حتى هذا التاريخ حيث بدأت الأعمال في جبل سمعان بتاريخ 31/8/2026 وبلغت نسبة الإنجاز للمشروع  32% وبحاجة إلى صرف المستحقات المالية لقاء هذه الأعمال 
+2- ارتفاع أسعار المحروقات بنسبة 40%
+ بلغت كمية الانقاض المرحلة قبل ارتفاع سعر المحروقات اي منذ بدء العمل حتى 12/9/2026 في اعزاز 12857م3 وساعات تهذيب المكب /8/ اما في جبل سمعان بلغت الكمية 65374م3
+وساعات تهذيب المكب /51/
+بلغت كمية الانقاض المرحلة بعد ارتفاع سعر المحروقات من 13/9/2026 ولغاية اليوم 11/10/2026 في اعزاز 39280م3 وساعات تهذيب المكب /3/اما في جبل سمعان 78917م3 
+وساعات تهذيب المكب /19/
+3-تم استئناف العمل في كل من اعزاز وجبل سمعان بتاريخ 17/10/2026                                                                                                                                      يوجد 4 نقاط متوقفة عن العمل بسبب انقطاع مادة المازوت بتاريخ 25/10/2026</t>
+  </si>
+  <si>
+    <t>بتاريخ 19/10/2026 تم انطلاق العمل في جسر الشغور وادلب ومن المتوقع البدء بمعرة النعمان وخان شيخون</t>
   </si>
   <si>
     <t xml:space="preserve">اجمالي المرحلة الثالثة </t>
@@ -151,59 +160,60 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="20"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -375,39 +385,42 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="40" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="40" fontId="8" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -415,40 +428,40 @@
     <xf numFmtId="40" fontId="8" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
-    <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -662,43 +675,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" customWidth="1"/>
-    <col min="6" max="6" width="116.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="24.875" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="21.75" customWidth="1"/>
+    <col min="6" max="6" width="138.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:6" ht="14.25">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+    </row>
+    <row r="2" spans="1:6" ht="14.25">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
     </row>
     <row r="3" spans="1:6" ht="26.45" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="19">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
-      </c>
-      <c r="C3" s="19"/>
+        <v>46323</v>
+      </c>
+      <c r="C3" s="20"/>
     </row>
     <row r="4" spans="1:6" ht="26.45" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -721,7 +734,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="37.9" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="21" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -742,7 +755,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="37.9" customHeight="1">
-      <c r="A6" s="21"/>
+      <c r="A6" s="22"/>
       <c r="B6" s="6" t="s">
         <v>11</v>
       </c>
@@ -753,7 +766,7 @@
         <v>56798</v>
       </c>
       <c r="E6" s="8">
-        <f t="shared" ref="E6:E19" si="0">D6/C6</f>
+        <f t="shared" ref="E6:E18" si="0">D6/C6</f>
         <v>1.0032500794856396</v>
       </c>
       <c r="F6" s="7" t="s">
@@ -761,7 +774,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="37.9" customHeight="1">
-      <c r="A7" s="22"/>
+      <c r="A7" s="23"/>
       <c r="B7" s="6" t="s">
         <v>12</v>
       </c>
@@ -780,10 +793,10 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="37.9" customHeight="1">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="16"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="10">
         <f>SUM(C5:C7)</f>
         <v>1059985</v>
@@ -799,7 +812,7 @@
       <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:6" ht="37.9" customHeight="1">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="21" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -815,12 +828,12 @@
         <f t="shared" si="0"/>
         <v>1.0011505925250683</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="54" customHeight="1">
-      <c r="A10" s="21"/>
+      <c r="A10" s="22"/>
       <c r="B10" s="6" t="s">
         <v>17</v>
       </c>
@@ -834,12 +847,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="37.9" customHeight="1">
-      <c r="A11" s="21"/>
+      <c r="A11" s="22"/>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
@@ -847,18 +860,18 @@
         <v>641500</v>
       </c>
       <c r="D11" s="6">
-        <v>610539</v>
+        <v>624377</v>
       </c>
       <c r="E11" s="8">
         <f t="shared" si="0"/>
-        <v>0.95173655494933751</v>
-      </c>
-      <c r="F11" s="7" t="s">
+        <v>0.9733078721745908</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="37.9" customHeight="1">
-      <c r="A12" s="22"/>
+    <row r="12" spans="1:6" ht="93.75" customHeight="1">
+      <c r="A12" s="23"/>
       <c r="B12" s="6" t="s">
         <v>11</v>
       </c>
@@ -866,37 +879,37 @@
         <v>50000</v>
       </c>
       <c r="D12" s="6">
-        <v>22778</v>
+        <v>39823</v>
       </c>
       <c r="E12" s="8">
         <f t="shared" si="0"/>
-        <v>0.45556000000000002</v>
-      </c>
-      <c r="F12" s="7" t="s">
+        <v>0.79645999999999995</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="37.9" customHeight="1">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="16"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="10">
         <f>SUM(C9:C12)</f>
         <v>1565075</v>
       </c>
       <c r="D13" s="10">
         <f>SUM(D9:D12)</f>
-        <v>1182448.1000000001</v>
+        <v>1213331.1000000001</v>
       </c>
       <c r="E13" s="8">
         <f t="shared" ref="E13" si="1">D13/C13</f>
-        <v>0.75552168426433242</v>
-      </c>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="1:6" ht="37.9" customHeight="1">
-      <c r="A14" s="20" t="s">
+        <v>0.77525428493842152</v>
+      </c>
+      <c r="F13" s="11"/>
+    </row>
+    <row r="14" spans="1:6" ht="95.25" customHeight="1">
+      <c r="A14" s="21" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -909,15 +922,15 @@
         <v>0</v>
       </c>
       <c r="E14" s="8">
-        <f t="shared" si="0"/>
+        <f>D14/C14</f>
         <v>0</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="56.25" customHeight="1">
-      <c r="A15" s="21"/>
+      <c r="A15" s="22"/>
       <c r="B15" s="6" t="s">
         <v>25</v>
       </c>
@@ -931,12 +944,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="11" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="90" customHeight="1">
-      <c r="A16" s="21"/>
+      <c r="A16" s="22"/>
       <c r="B16" s="6" t="s">
         <v>12</v>
       </c>
@@ -950,12 +963,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="98.25" customHeight="1">
-      <c r="A17" s="21"/>
+    <row r="17" spans="1:6" ht="127.5" customHeight="1">
+      <c r="A17" s="22"/>
       <c r="B17" s="6" t="s">
         <v>28</v>
       </c>
@@ -969,12 +982,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="11" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="60.75" customHeight="1">
-      <c r="A18" s="21"/>
+    <row r="18" spans="1:6" ht="321.75">
+      <c r="A18" s="22"/>
       <c r="B18" s="6" t="s">
         <v>15</v>
       </c>
@@ -982,18 +995,18 @@
         <v>600000</v>
       </c>
       <c r="D18" s="6">
-        <v>194377</v>
+        <v>255597</v>
       </c>
       <c r="E18" s="8">
         <f t="shared" si="0"/>
-        <v>0.32396166666666665</v>
-      </c>
-      <c r="F18" s="7" t="s">
+        <v>0.42599500000000001</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="37.9" customHeight="1">
-      <c r="A19" s="21"/>
+      <c r="A19" s="22"/>
       <c r="B19" s="6" t="s">
         <v>9</v>
       </c>
@@ -1001,56 +1014,60 @@
         <v>650000</v>
       </c>
       <c r="D19" s="6">
-        <v>0</v>
+        <v>68655</v>
       </c>
       <c r="E19" s="8">
         <f>D19/C19</f>
-        <v>0</v>
+        <v>0.10562307692307692</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="37.9" customHeight="1">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="16"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="10">
         <f>SUM(C14:C19)</f>
         <v>2843744</v>
       </c>
       <c r="D20" s="10">
         <f>SUM(D14:D19)</f>
-        <v>194377</v>
+        <v>324252</v>
       </c>
       <c r="E20" s="8">
         <f t="shared" ref="E20:E21" si="2">D20/C20</f>
-        <v>6.8352495864606663E-2</v>
+        <v>0.11402292189451653</v>
       </c>
       <c r="F20" s="7"/>
     </row>
     <row r="21" spans="1:6" ht="56.25" customHeight="1">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="11">
+      <c r="B21" s="15"/>
+      <c r="C21" s="12">
         <f>C8+C13+C20</f>
         <v>5468804</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="13">
         <f>D8+D13+D20</f>
-        <v>2580680.1</v>
+        <v>2741438.1</v>
       </c>
       <c r="E21" s="8">
         <f t="shared" si="2"/>
-        <v>0.47189113012644085</v>
+        <v>0.50128658843871532</v>
       </c>
       <c r="F21" s="9"/>
     </row>
-    <row r="22" spans="1:6" ht="15"/>
-    <row r="23" spans="1:6" ht="15"/>
+    <row r="23" spans="1:6">
+      <c r="D23">
+        <f>D5+D11</f>
+        <v>1330063</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A21:B21"/>
@@ -1078,7 +1095,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="36" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
